--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate/AGGREGATE_COTO CÓRDOBA CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate/AGGREGATE_COTO CÓRDOBA CB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE58"/>
+  <dimension ref="A1:BA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,81 +639,6 @@
           <t>Gen/TO</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 37</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 49</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 50</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 51</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -722,16 +647,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1898.6</v>
+        <v>1865.6</v>
       </c>
       <c r="C2" t="n">
-        <v>1906.92</v>
+        <v>1884.42</v>
       </c>
       <c r="D2" t="n">
-        <v>102.4164621483859</v>
+        <v>103.639316076034</v>
       </c>
       <c r="E2" t="n">
-        <v>97.38216600591532</v>
+        <v>98.54491037029963</v>
       </c>
       <c r="F2" t="n">
         <v>0.4968213604577241</v>
@@ -740,19 +665,19 @@
         <v>0.1666975365808483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3049065420560748</v>
+        <v>0.3352337514253136</v>
       </c>
       <c r="I2" t="n">
         <v>0.2479338842975207</v>
       </c>
       <c r="J2" t="n">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="L2" t="n">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="M2" t="n">
         <v>168</v>
@@ -827,13 +752,13 @@
         <v>0.9639769452449568</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7247191011235955</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9578544061302682</v>
+        <v>0.6020408163265306</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.959375</v>
+        <v>1.912162162162162</v>
       </c>
       <c r="AN2" t="n">
         <v>0.8472222222222222</v>
@@ -843,51 +768,6 @@
       </c>
       <c r="AP2" t="n">
         <v>5.216666666666667</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -897,16 +777,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.02307692307691</v>
+        <v>71.75384615384615</v>
       </c>
       <c r="C3" t="n">
-        <v>73.34307692307691</v>
+        <v>72.47769230769229</v>
       </c>
       <c r="D3" t="n">
-        <v>102.4164621483859</v>
+        <v>103.639316076034</v>
       </c>
       <c r="E3" t="n">
-        <v>97.38216600591532</v>
+        <v>98.54491037029963</v>
       </c>
       <c r="F3" t="n">
         <v>0.4968213604577241</v>
@@ -915,19 +795,19 @@
         <v>0.1666975365808483</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3049065420560748</v>
+        <v>0.3352337514253136</v>
       </c>
       <c r="I3" t="n">
         <v>0.2479338842975207</v>
       </c>
       <c r="J3" t="n">
-        <v>9.923076923076923</v>
+        <v>8.615384615384615</v>
       </c>
       <c r="K3" t="n">
-        <v>9.615384615384615</v>
+        <v>6.807692307692307</v>
       </c>
       <c r="L3" t="n">
-        <v>11.80769230769231</v>
+        <v>10.88461538461539</v>
       </c>
       <c r="M3" t="n">
         <v>6.461538461538462</v>
@@ -1002,13 +882,13 @@
         <v>0.9639769452449567</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7247191011235956</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9578544061302682</v>
+        <v>0.6020408163265305</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.959375</v>
+        <v>1.912162162162162</v>
       </c>
       <c r="AN3" t="n">
         <v>0.8472222222222221</v>
@@ -1018,51 +898,6 @@
       </c>
       <c r="AP3" t="n">
         <v>5.216666666666666</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1072,16 +907,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1915.24</v>
+        <v>1903.24</v>
       </c>
       <c r="C4" t="n">
-        <v>1906.92</v>
+        <v>1884.42</v>
       </c>
       <c r="D4" t="n">
-        <v>97.38216600591532</v>
+        <v>98.54491037029963</v>
       </c>
       <c r="E4" t="n">
-        <v>102.4164621483859</v>
+        <v>103.639316076034</v>
       </c>
       <c r="F4" t="n">
         <v>0.4621019108280255</v>
@@ -1090,19 +925,19 @@
         <v>0.1626878221767265</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2932330827067669</v>
+        <v>0.3131868131868132</v>
       </c>
       <c r="I4" t="n">
         <v>0.2585987261146497</v>
       </c>
       <c r="J4" t="n">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="L4" t="n">
-        <v>332</v>
+        <v>275</v>
       </c>
       <c r="M4" t="n">
         <v>161</v>
@@ -1177,13 +1012,13 @@
         <v>0.9121338912133892</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6138888888888889</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5754385964912281</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9378531073446328</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AN4" t="n">
         <v>0.797752808988764</v>
@@ -1193,51 +1028,6 @@
       </c>
       <c r="AP4" t="n">
         <v>5.207865168539326</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1247,16 +1037,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.66307692307693</v>
+        <v>73.20153846153848</v>
       </c>
       <c r="C5" t="n">
-        <v>73.34307692307691</v>
+        <v>72.47769230769229</v>
       </c>
       <c r="D5" t="n">
-        <v>97.38216600591532</v>
+        <v>98.54491037029963</v>
       </c>
       <c r="E5" t="n">
-        <v>102.4164621483859</v>
+        <v>103.639316076034</v>
       </c>
       <c r="F5" t="n">
         <v>0.4621019108280254</v>
@@ -1265,19 +1055,19 @@
         <v>0.1626878221767265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2932330827067669</v>
+        <v>0.3131868131868132</v>
       </c>
       <c r="I5" t="n">
         <v>0.2585987261146497</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>6.307692307692307</v>
       </c>
       <c r="L5" t="n">
-        <v>12.76923076923077</v>
+        <v>10.57692307692308</v>
       </c>
       <c r="M5" t="n">
         <v>6.192307692307693</v>
@@ -1352,13 +1142,13 @@
         <v>0.9121338912133889</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6138888888888888</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5754385964912281</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9378531073446329</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AN5" t="n">
         <v>0.7977528089887641</v>
@@ -1368,51 +1158,6 @@
       </c>
       <c r="AP5" t="n">
         <v>5.207865168539326</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1711,10 +1456,10 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>6</v>
@@ -1735,22 +1480,22 @@
         <v>15</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
@@ -1833,10 +1578,10 @@
         <v>0.181</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.078</v>
+        <v>0.074</v>
       </c>
       <c r="BA8" t="n">
         <v>0.017</v>
@@ -1876,10 +1621,10 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>3</v>
@@ -1888,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>7</v>
@@ -1900,10 +1645,10 @@
         <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="U9" t="n">
         <v>13</v>
@@ -1915,7 +1660,7 @@
         <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
@@ -1998,10 +1743,10 @@
         <v>0.25</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.154</v>
+        <v>0.145</v>
       </c>
       <c r="BA9" t="n">
         <v>0.003</v>
@@ -2053,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
         <v>32</v>
@@ -2065,22 +1810,22 @@
         <v>46</v>
       </c>
       <c r="S10" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="U10" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Y10" t="n">
         <v>25</v>
@@ -2166,7 +1911,7 @@
         <v>0.014</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="BA10" t="n">
         <v>0.058</v>
@@ -2230,22 +1975,22 @@
         <v>38</v>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="U11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
         <v>12</v>
@@ -2331,7 +2076,7 @@
         <v>0.029</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="BA11" t="n">
         <v>0.038</v>
@@ -2371,10 +2116,10 @@
         <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
@@ -2395,22 +2140,22 @@
         <v>62</v>
       </c>
       <c r="S12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="U12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="X12" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
         <v>26</v>
@@ -2493,10 +2238,10 @@
         <v>0.194</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.097</v>
+        <v>0.108</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.246</v>
+        <v>0.239</v>
       </c>
       <c r="BA12" t="n">
         <v>0.036</v>
@@ -2536,10 +2281,10 @@
         <v>87</v>
       </c>
       <c r="K13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
         <v>21</v>
@@ -2548,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>57</v>
@@ -2560,22 +2305,22 @@
         <v>78</v>
       </c>
       <c r="S13" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="U13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="V13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="W13" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="X13" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>32</v>
@@ -2658,10 +2403,10 @@
         <v>0.231</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.132</v>
+        <v>0.133</v>
       </c>
       <c r="BA13" t="n">
         <v>0.145</v>
@@ -2713,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>10</v>
@@ -2725,22 +2470,22 @@
         <v>37</v>
       </c>
       <c r="S14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="U14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
         <v>4</v>
@@ -2823,10 +2568,10 @@
         <v>0.235</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="BA14" t="n">
         <v>0.028</v>
@@ -2866,10 +2611,10 @@
         <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M15" t="n">
         <v>9</v>
@@ -2890,22 +2635,22 @@
         <v>69</v>
       </c>
       <c r="S15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="W15" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="n">
         <v>45</v>
@@ -2988,10 +2733,10 @@
         <v>0.212</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.133</v>
+        <v>0.137</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="BA15" t="n">
         <v>0.028</v>
@@ -3031,10 +2776,10 @@
         <v>51</v>
       </c>
       <c r="K16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M16" t="n">
         <v>16</v>
@@ -3043,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
         <v>47</v>
@@ -3055,22 +2800,22 @@
         <v>43</v>
       </c>
       <c r="S16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="U16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W16" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="X16" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
@@ -3153,10 +2898,10 @@
         <v>0.236</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.08</v>
+        <v>0.076</v>
       </c>
       <c r="BA16" t="n">
         <v>0.082</v>
@@ -3196,10 +2941,10 @@
         <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
@@ -3220,22 +2965,22 @@
         <v>84</v>
       </c>
       <c r="S17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="U17" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>15</v>
+      </c>
+      <c r="X17" t="n">
         <v>10</v>
-      </c>
-      <c r="V17" t="n">
-        <v>14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
@@ -3318,10 +3063,10 @@
         <v>0.172</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="BA17" t="n">
         <v>0.006</v>
@@ -3361,10 +3106,10 @@
         <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L18" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
         <v>31</v>
@@ -3373,7 +3118,7 @@
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>21</v>
@@ -3385,22 +3130,22 @@
         <v>56</v>
       </c>
       <c r="S18" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="U18" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="V18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="X18" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
         <v>27</v>
@@ -3483,10 +3228,10 @@
         <v>0.142</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
         <v>0.035</v>
@@ -3526,10 +3271,10 @@
         <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L19" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
         <v>22</v>
@@ -3550,22 +3295,22 @@
         <v>48</v>
       </c>
       <c r="S19" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="U19" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="V19" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X19" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
         <v>19</v>
@@ -3648,10 +3393,10 @@
         <v>0.225</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.065</v>
+        <v>0.093</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.165</v>
+        <v>0.141</v>
       </c>
       <c r="BA19" t="n">
         <v>0.028</v>
@@ -3715,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -3813,10 +3558,10 @@
         <v>0.25</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.299</v>
+        <v>0.306</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -3856,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -3871,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3948,7 +3693,7 @@
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -3990,163 +3735,163 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="K22" t="n">
-        <v>26</v>
+        <v>625</v>
       </c>
       <c r="L22" t="n">
-        <v>21</v>
+        <v>294</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>5225:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>2159.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.543</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>0.847</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>4.369</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>5.217</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -4155,122 +3900,122 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>1953</v>
+        <v>1857</v>
       </c>
       <c r="D23" t="n">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="E23" t="n">
-        <v>879</v>
+        <v>853</v>
       </c>
       <c r="F23" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G23" t="n">
-        <v>694</v>
+        <v>717</v>
       </c>
       <c r="H23" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="I23" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="J23" t="n">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K23" t="n">
-        <v>658</v>
+        <v>583</v>
       </c>
       <c r="L23" t="n">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="M23" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N23" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="O23" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P23" t="n">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q23" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="R23" t="n">
-        <v>588</v>
+        <v>507</v>
       </c>
       <c r="S23" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1870</v>
+        <v>1150</v>
       </c>
       <c r="U23" t="n">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="V23" t="n">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="W23" t="n">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="X23" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="Y23" t="n">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="Z23" t="n">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.624</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AB23" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="AC23" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.488</v>
+        <v>0.442</v>
       </c>
       <c r="AE23" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="AF23" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="AH23" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AI23" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.294</v>
+        <v>0.322</v>
       </c>
       <c r="AK23" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="AL23" t="n">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.335</v>
+        <v>0.296</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4278,40 +4023,40 @@
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>2159.6</v>
+        <v>2188.24</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.497</v>
+        <v>0.462</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.543</v>
+        <v>0.507</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.904</v>
+        <v>0.849</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.167</v>
+        <v>0.163</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.248</v>
+        <v>0.259</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.847</v>
+        <v>0.798</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.369</v>
+        <v>4.41</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.217</v>
+        <v>5.208</v>
       </c>
       <c r="AX23" t="n">
         <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.141</v>
+        <v>0.133</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4320,1340 +4065,1234 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>26</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1857</v>
-      </c>
-      <c r="D24" t="n">
-        <v>400</v>
-      </c>
-      <c r="E24" t="n">
-        <v>853</v>
-      </c>
-      <c r="F24" t="n">
-        <v>217</v>
-      </c>
-      <c r="G24" t="n">
-        <v>717</v>
-      </c>
-      <c r="H24" t="n">
-        <v>406</v>
-      </c>
-      <c r="I24" t="n">
-        <v>596</v>
-      </c>
-      <c r="J24" t="n">
-        <v>284</v>
-      </c>
-      <c r="K24" t="n">
-        <v>595</v>
-      </c>
-      <c r="L24" t="n">
-        <v>273</v>
-      </c>
-      <c r="M24" t="n">
-        <v>192</v>
-      </c>
-      <c r="N24" t="n">
-        <v>42</v>
-      </c>
-      <c r="O24" t="n">
-        <v>47</v>
-      </c>
-      <c r="P24" t="n">
-        <v>356</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>161</v>
-      </c>
-      <c r="R24" t="n">
-        <v>507</v>
-      </c>
-      <c r="S24" t="n">
-        <v>580</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1731</v>
-      </c>
-      <c r="U24" t="n">
-        <v>260</v>
-      </c>
-      <c r="V24" t="n">
-        <v>234</v>
-      </c>
-      <c r="W24" t="n">
-        <v>332</v>
-      </c>
-      <c r="X24" t="n">
-        <v>354</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>189</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>339</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>156</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>353</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>52</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>159</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>73</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>227</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>145</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>490</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>5225:00</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>2188.24</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.208</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LOBE HUESCA LA MAGIA</t>
+          <t>#1 L. SORENSEN (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3.462</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.846</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>5.825</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>#2 D. ROLLINS (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>4.167</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.417</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.083</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.917</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.019</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>5.571</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>5.857</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>BIELE ISB</t>
+          <t>#4 J. BLACK (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>12.269</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>3.077</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.385</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6.423</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.115</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.577</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.269</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2.538</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.769</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.692</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.346</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.038</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.731</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>4.538</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>11.865</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.034</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>#7 A. RODRIGUEZ AGUILAR (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>7.385</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2.308</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3.692</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2.692</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.423</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.192</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.484</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>27:15</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>7.038</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.049</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.437</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>11.188</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>CLASS BASQUET SANT ANTONI</t>
+          <t>#8 S. NDIAYE (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>6.462</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.731</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.615</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>3.731</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.615</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.385</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.615</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.619</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.038</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>7.189</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>0.899</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.618</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>4.265</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>COTO CÓRDOBA CB</t>
+          <t>#10 G. OROZCO DOMINGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>8.385</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.962</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>4.538</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.269</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.154</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.538</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.346</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.192</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.038</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.154</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.731</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>10.117</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>0.829</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.526</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3.105</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>4.632</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
+          <t>#11 A. OROZCO DOMINGUEZ (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4.077</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1.538</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3.154</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.423</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.346</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>5.331</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
+          <t>#15 K. SCHUTTE (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>8.077</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>5.462</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5662,82 +5301,82 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2.808</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.077</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.654</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.731</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.654</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>0.652</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.077</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -5759,4230 +5398,1366 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>7.898</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>0.651</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.023</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>3.227</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>3.591</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+          <t>#16 P. SANCHEZ INFANTES (Per Game)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.385</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.808</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.808</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>73</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>8.465999999999999</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0.082</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#1 L. SORENSEN (Per Game)</t>
+          <t>#17 N. SAGNIA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>3.462</v>
+        <v>3.885</v>
       </c>
       <c r="D34" t="n">
-        <v>1.077</v>
+        <v>1.423</v>
       </c>
       <c r="E34" t="n">
-        <v>2.769</v>
+        <v>3.308</v>
       </c>
       <c r="F34" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.846</v>
+        <v>0.115</v>
       </c>
       <c r="H34" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AB34" t="n">
         <v>0.615</v>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="O34" t="n">
-        <v>5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AC34" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.154</v>
       </c>
-      <c r="S34" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="T34" t="n">
-        <v>26</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.923</v>
-      </c>
       <c r="AG34" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.538</v>
+        <v>0.077</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.308</v>
+        <v>0.038</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.825</v>
+        <v>5.446</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.308</v>
+        <v>0.416</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.342</v>
+        <v>0.474</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.594</v>
+        <v>0.713</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.132</v>
+        <v>0.247</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.133</v>
+        <v>0.303</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.1</v>
+        <v>0.114</v>
       </c>
       <c r="AV34" t="n">
-        <v>6</v>
+        <v>2.543</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.1</v>
+        <v>2.657</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.181</v>
+        <v>0.172</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.078</v>
+        <v>0.13</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.035</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#2 D. ROLLINS (Per Game)</t>
+          <t>#27 F. BELLO MOURE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
-        <v>4.167</v>
+        <v>6.577</v>
       </c>
       <c r="D35" t="n">
-        <v>0.417</v>
+        <v>1.808</v>
       </c>
       <c r="E35" t="n">
-        <v>0.833</v>
+        <v>2.462</v>
       </c>
       <c r="F35" t="n">
-        <v>0.917</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>2.417</v>
+        <v>2.308</v>
       </c>
       <c r="H35" t="n">
-        <v>0.583</v>
+        <v>0.885</v>
       </c>
       <c r="I35" t="n">
-        <v>0.583</v>
+        <v>1.308</v>
       </c>
       <c r="J35" t="n">
-        <v>0.167</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>1.083</v>
+        <v>2.192</v>
       </c>
       <c r="L35" t="n">
-        <v>0.083</v>
+        <v>1.654</v>
       </c>
       <c r="M35" t="n">
-        <v>0.25</v>
+        <v>1.192</v>
       </c>
       <c r="N35" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0.583</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.167</v>
+        <v>0.385</v>
       </c>
       <c r="R35" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>176</v>
+      </c>
+      <c r="U35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.5</v>
       </c>
-      <c r="T35" t="n">
-        <v>34</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>6.152</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AU35" t="n">
         <v>1</v>
       </c>
-      <c r="AH35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.917</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0.286</v>
-      </c>
       <c r="AV35" t="n">
-        <v>5.571</v>
+        <v>5.905</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.857</v>
+        <v>6.905</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.25</v>
+        <v>0.142</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.013</v>
+        <v>0.094</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.154</v>
+        <v>0.12</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.007</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#4 J. BLACK (Per Game)</t>
+          <t>#35 J. SIENCHE GUEMETA (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>26</v>
       </c>
       <c r="C36" t="n">
-        <v>12.269</v>
+        <v>7.885</v>
       </c>
       <c r="D36" t="n">
-        <v>1.5</v>
+        <v>1.692</v>
       </c>
       <c r="E36" t="n">
-        <v>3.077</v>
+        <v>3.308</v>
       </c>
       <c r="F36" t="n">
-        <v>2.385</v>
+        <v>0.846</v>
       </c>
       <c r="G36" t="n">
-        <v>6.423</v>
+        <v>2.462</v>
       </c>
       <c r="H36" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.115</v>
       </c>
-      <c r="I36" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.538</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.269</v>
+        <v>1.346</v>
       </c>
       <c r="M36" t="n">
-        <v>1.115</v>
+        <v>0.846</v>
       </c>
       <c r="N36" t="n">
-        <v>0.038</v>
+        <v>0.077</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
         <v>1.231</v>
       </c>
       <c r="Q36" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.846</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>156</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AK36" t="n">
         <v>0.5</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.769</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.154</v>
-      </c>
-      <c r="T36" t="n">
-        <v>270</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.077</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.346</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.885</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.731</v>
-      </c>
       <c r="AL36" t="n">
-        <v>4.538</v>
+        <v>1.231</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.381</v>
+        <v>0.406</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>11.865</v>
+        <v>8.032</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.534</v>
+        <v>0.513</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.577</v>
+        <v>0.58</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.034</v>
+        <v>0.982</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.104</v>
+        <v>0.153</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.223</v>
+        <v>0.34</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.031</v>
+        <v>0.531</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.719</v>
+        <v>4.688</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.75</v>
+        <v>5.219</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.25</v>
+        <v>0.225</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.014</v>
+        <v>0.093</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.058</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#7 A. RODRIGUEZ AGUILAR (Per Game)</t>
+          <t>#90 J. BAENA DELGADO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>7.385</v>
+        <v>0.167</v>
       </c>
       <c r="D37" t="n">
-        <v>1.115</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.308</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.462</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>3.692</v>
+        <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>0.769</v>
+        <v>0.167</v>
       </c>
       <c r="I37" t="n">
-        <v>0.962</v>
+        <v>0.167</v>
       </c>
       <c r="J37" t="n">
-        <v>0.885</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.692</v>
+        <v>0.167</v>
       </c>
       <c r="L37" t="n">
-        <v>0.654</v>
+        <v>0.083</v>
       </c>
       <c r="M37" t="n">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.346</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.462</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.231</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>201</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.154</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.885</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.846</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.577</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.077</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.231</v>
+        <v>0.083</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.192</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.462</v>
+        <v>0.167</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>27:15</t>
+          <t>00:37</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>7.038</v>
+        <v>0.323</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.575</v>
+        <v>0.258</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.049</v>
+        <v>0.515</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.128</v>
+        <v>0.667</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.437</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>11.188</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.029</v>
+        <v>0.159</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.111</v>
+        <v>0.306</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#8 S. NDIAYE (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>26</v>
       </c>
       <c r="C38" t="n">
-        <v>6.462</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2.038</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3.731</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.692</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2.615</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L38" t="n">
         <v>0.846</v>
       </c>
-      <c r="K38" t="n">
-        <v>3.923</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.423</v>
-      </c>
       <c r="M38" t="n">
-        <v>0.846</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.308</v>
+        <v>0.577</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="R38" t="n">
-        <v>2.385</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.231</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.885</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.615</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.346</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.615</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.577</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.038</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.077</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>7.189</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.899</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.618</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.265</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.246</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#10 G. OROZCO DOMINGUEZ (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>26</v>
       </c>
       <c r="C39" t="n">
-        <v>8.385</v>
+        <v>75.11499999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>1.962</v>
+        <v>17.192</v>
       </c>
       <c r="E39" t="n">
-        <v>4.538</v>
+        <v>33.808</v>
       </c>
       <c r="F39" t="n">
-        <v>0.769</v>
+        <v>8.577</v>
       </c>
       <c r="G39" t="n">
-        <v>2.269</v>
+        <v>26.692</v>
       </c>
       <c r="H39" t="n">
-        <v>2.154</v>
+        <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>2.538</v>
+        <v>19.808</v>
       </c>
       <c r="J39" t="n">
-        <v>3.346</v>
+        <v>11.731</v>
       </c>
       <c r="K39" t="n">
-        <v>2.5</v>
+        <v>24.038</v>
       </c>
       <c r="L39" t="n">
-        <v>0.538</v>
+        <v>11.308</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8080000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0.346</v>
+        <v>1.808</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="P39" t="n">
-        <v>2.192</v>
+        <v>13.846</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.8080000000000001</v>
+        <v>6.462</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>22.615</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>221</v>
+        <v>1371</v>
       </c>
       <c r="U39" t="n">
-        <v>1.231</v>
+        <v>8.615</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>6.808</v>
       </c>
       <c r="W39" t="n">
-        <v>1.462</v>
+        <v>10.885</v>
       </c>
       <c r="X39" t="n">
-        <v>2.038</v>
+        <v>5.692</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.231</v>
+        <v>8.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.154</v>
+        <v>13.615</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.571</v>
+        <v>0.624</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.615</v>
+        <v>6.346</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.885</v>
+        <v>13</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.327</v>
+        <v>0.488</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.115</v>
+        <v>2.346</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.5</v>
+        <v>7.192</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.231</v>
+        <v>0.326</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.077</v>
+        <v>2.615</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.538</v>
+        <v>8.885</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.143</v>
+        <v>0.294</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.6919999999999999</v>
+        <v>5.962</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.731</v>
+        <v>17.808</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.4</v>
+        <v>0.335</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>200:57</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>10.117</v>
+        <v>83.062</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.458</v>
+        <v>0.497</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.529</v>
+        <v>0.543</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.829</v>
+        <v>0.904</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.217</v>
+        <v>0.167</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.316</v>
+        <v>0.248</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.526</v>
+        <v>0.847</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.105</v>
+        <v>4.369</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.632</v>
+        <v>5.217</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.231</v>
+        <v>0.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.031</v>
+        <v>0.067</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#11 A. OROZCO DOMINGUEZ (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>26</v>
       </c>
       <c r="C40" t="n">
-        <v>4.077</v>
+        <v>71.423</v>
       </c>
       <c r="D40" t="n">
-        <v>0.423</v>
+        <v>15.385</v>
       </c>
       <c r="E40" t="n">
-        <v>1.538</v>
+        <v>32.808</v>
       </c>
       <c r="F40" t="n">
-        <v>0.885</v>
+        <v>8.346</v>
       </c>
       <c r="G40" t="n">
-        <v>3.154</v>
+        <v>27.577</v>
       </c>
       <c r="H40" t="n">
-        <v>0.577</v>
+        <v>15.615</v>
       </c>
       <c r="I40" t="n">
-        <v>0.577</v>
+        <v>22.923</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6919999999999999</v>
+        <v>10.923</v>
       </c>
       <c r="K40" t="n">
-        <v>0.615</v>
+        <v>22.423</v>
       </c>
       <c r="L40" t="n">
-        <v>0.077</v>
+        <v>10.962</v>
       </c>
       <c r="M40" t="n">
+        <v>7.385</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="O40" t="n">
+        <v>48</v>
+      </c>
+      <c r="P40" t="n">
+        <v>13.692</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.192</v>
+      </c>
+      <c r="R40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1150</v>
+      </c>
+      <c r="U40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6.308</v>
+      </c>
+      <c r="W40" t="n">
+        <v>10.577</v>
+      </c>
+      <c r="X40" t="n">
+        <v>5.769</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.269</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>13.038</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>13.577</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>6.115</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.808</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>8.731</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>5.577</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>18.846</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>200:57</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>84.163</v>
+      </c>
+      <c r="AP40" t="n">
         <v>0.462</v>
       </c>
-      <c r="N40" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="T40" t="n">
-        <v>34</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.346</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>5.331</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.373</v>
-      </c>
       <c r="AQ40" t="n">
-        <v>0.412</v>
+        <v>0.507</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.765</v>
+        <v>0.849</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.163</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.123</v>
+        <v>0.259</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.8</v>
+        <v>0.798</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.2</v>
+        <v>4.41</v>
       </c>
       <c r="AW40" t="n">
-        <v>14</v>
+        <v>5.208</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.235</v>
+        <v>0.203</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.063</v>
+        <v>0.128</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>#15 K. SCHUTTE (Per Game)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>26</v>
-      </c>
-      <c r="C41" t="n">
-        <v>8.077</v>
-      </c>
-      <c r="D41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5.462</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2.923</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="O41" t="n">
-        <v>6</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.769</v>
-      </c>
-      <c r="T41" t="n">
-        <v>226</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.308</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.077</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>7.898</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.227</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>3.591</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>#16 P. SANCHEZ INFANTES (Per Game)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>26</v>
-      </c>
-      <c r="C42" t="n">
-        <v>6.385</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.308</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3.115</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2.077</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2.808</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="T42" t="n">
-        <v>143</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>8.465999999999999</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.085</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>4.085</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>#17 N. SAGNIA (Per Game)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>26</v>
-      </c>
-      <c r="C43" t="n">
-        <v>3.885</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3.308</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.538</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.346</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.231</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="T43" t="n">
-        <v>63</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>5.446</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.543</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>2.657</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>#27 F. BELLO MOURE (Per Game)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>26</v>
-      </c>
-      <c r="C44" t="n">
-        <v>6.577</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2.462</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2.308</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.308</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.423</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2.154</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="T44" t="n">
-        <v>212</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.577</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.538</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>20:54</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>6.152</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.069</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>5.905</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>6.905</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>#35 J. SIENCHE GUEMETA (Per Game)</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>26</v>
-      </c>
-      <c r="C45" t="n">
-        <v>7.885</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.308</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.462</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.346</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.538</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="O45" t="n">
-        <v>6</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="T45" t="n">
-        <v>207</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.538</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.615</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AO45" t="n">
-        <v>8.032</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>4.688</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>5.219</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>#90 J. BAENA DELGADO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>12</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>00:37</t>
-        </is>
-      </c>
-      <c r="AO46" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Equip (Per Game)</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>26</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO47" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>LOBE HUESCA LA MAGIA (Per Game)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>13</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>13</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Equip (Per Game)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>26</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>13</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>13</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>CLASS BASQUET SANT ANTONI (Per Game)</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>13</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN (Per Game)</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>13</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>BIELE ISB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>13</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ (Per Game)</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>13</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>26</v>
-      </c>
-      <c r="C57" t="n">
-        <v>75.11499999999999</v>
-      </c>
-      <c r="D57" t="n">
-        <v>17.192</v>
-      </c>
-      <c r="E57" t="n">
-        <v>33.808</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8.577</v>
-      </c>
-      <c r="G57" t="n">
-        <v>26.692</v>
-      </c>
-      <c r="H57" t="n">
-        <v>15</v>
-      </c>
-      <c r="I57" t="n">
-        <v>19.808</v>
-      </c>
-      <c r="J57" t="n">
-        <v>11.731</v>
-      </c>
-      <c r="K57" t="n">
-        <v>25.308</v>
-      </c>
-      <c r="L57" t="n">
-        <v>10.038</v>
-      </c>
-      <c r="M57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="O57" t="n">
-        <v>42</v>
-      </c>
-      <c r="P57" t="n">
-        <v>13.846</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>6.462</v>
-      </c>
-      <c r="R57" t="n">
-        <v>22.615</v>
-      </c>
-      <c r="S57" t="n">
-        <v>19.269</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1870</v>
-      </c>
-      <c r="U57" t="n">
-        <v>9.923</v>
-      </c>
-      <c r="V57" t="n">
-        <v>9.615</v>
-      </c>
-      <c r="W57" t="n">
-        <v>11.808</v>
-      </c>
-      <c r="X57" t="n">
-        <v>12.308</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>13.615</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>6.346</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.346</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>7.192</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>8.885</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>5.962</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>17.808</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>200:57</t>
-        </is>
-      </c>
-      <c r="AO57" t="n">
-        <v>83.062</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>4.369</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>5.217</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>26</v>
-      </c>
-      <c r="C58" t="n">
-        <v>71.423</v>
-      </c>
-      <c r="D58" t="n">
-        <v>15.385</v>
-      </c>
-      <c r="E58" t="n">
-        <v>32.808</v>
-      </c>
-      <c r="F58" t="n">
-        <v>8.346</v>
-      </c>
-      <c r="G58" t="n">
-        <v>27.577</v>
-      </c>
-      <c r="H58" t="n">
-        <v>15.615</v>
-      </c>
-      <c r="I58" t="n">
-        <v>22.923</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10.923</v>
-      </c>
-      <c r="K58" t="n">
-        <v>22.885</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7.385</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.615</v>
-      </c>
-      <c r="O58" t="n">
-        <v>47</v>
-      </c>
-      <c r="P58" t="n">
-        <v>13.692</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>6.192</v>
-      </c>
-      <c r="R58" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S58" t="n">
-        <v>22.308</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1731</v>
-      </c>
-      <c r="U58" t="n">
-        <v>10</v>
-      </c>
-      <c r="V58" t="n">
-        <v>9</v>
-      </c>
-      <c r="W58" t="n">
-        <v>12.769</v>
-      </c>
-      <c r="X58" t="n">
-        <v>13.615</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>7.269</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>13.038</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>13.577</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>6.115</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>2.808</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>8.731</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>5.577</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>18.846</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>200:57</t>
-        </is>
-      </c>
-      <c r="AO58" t="n">
-        <v>84.163</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>5.208</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="BA58" t="n">
         <v>0</v>
       </c>
     </row>
